--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rf9f2ddd906524653"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R19136d20214a41f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R184b8bb86a8945e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R2b70e9082d164334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="Re3753fef95d7478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Rb1d2ae9ebdf34d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R74af03ca2194480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R6c1066e5a3fe4416"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R21eed9f940094626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R4c2160cd1ff749cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R1a3a3528c5bf4a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Rff765057d3a94275"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R70c7567a16ae4cbc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6a182a4fb68499d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rba51b45c0ad6495a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d7533e3d8684e72"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18718,7 +18718,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7555c49157884b92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cb36700d14945ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20282,7 +20282,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fa94b6e09c040c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1900a96b372d4bb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21028,7 +21028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff9d9a634dda4eb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5989c0bf6d0f4a2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21592,7 +21592,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6d717f19d547ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0aa19c2d184749"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21736,7 +21736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R287c545140fd407b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d1f51535f204a45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22363,6 +22363,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda6789cc82f343be"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8feffe0995b84fbb"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R74af03ca2194480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R6c1066e5a3fe4416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R21eed9f940094626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R4c2160cd1ff749cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R1a3a3528c5bf4a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Rff765057d3a94275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rb11b70f3f639409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rd5de988bbf6a4818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R3dabe34807924cb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="Reb71b2c39ce74c67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R1f4cdf68cd8b4de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Rc56f213c6e4140f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re6a182a4fb68499d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91b05a8c7b1b4233"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d7533e3d8684e72"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0680bfbfce29422a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18718,7 +18718,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cb36700d14945ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f16adf89ee498a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20282,7 +20282,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1900a96b372d4bb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9512e3d6dc7b4470"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21028,7 +21028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5989c0bf6d0f4a2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0dad73b6c584f92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21592,7 +21592,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0aa19c2d184749"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8922d4507a74821"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21736,7 +21736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d1f51535f204a45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2280c04413e4005"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22363,6 +22363,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8feffe0995b84fbb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ecaf16ca714519"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rb11b70f3f639409e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rd5de988bbf6a4818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R3dabe34807924cb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="Reb71b2c39ce74c67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R1f4cdf68cd8b4de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Rc56f213c6e4140f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rb115d8c259a945f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rd861521ed39b46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R9ea6ff093514478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R46e23c33f0e849c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="Rb9b70cdff9224ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="Re9c0b71d09304f59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91b05a8c7b1b4233"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5014139187614321"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0680bfbfce29422a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7e6a3e32b5b941df"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18718,7 +18718,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f16adf89ee498a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619be6f97b764625"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20282,7 +20282,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9512e3d6dc7b4470"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e22f634438d4dfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21028,7 +21028,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0dad73b6c584f92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra993201c7276473c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21592,7 +21592,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8922d4507a74821"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4c11f5288774d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21736,7 +21736,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2280c04413e4005"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdf8df0052f74b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22363,6 +22363,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ecaf16ca714519"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9c9bc959e284d7f"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R4a049bd13cd14f2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rdf00df1ca47c4d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="Rff19fa2328a940c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R02b236411c404636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R87ad41db9b3c4583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R57a9e4f2703b4878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Re8c4dd0368a24a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R3f38cfa91fb94d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="Rcaeb400338e14175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R9645a6048c3b4807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R26949708fc884499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R865ff47078384e27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R781b745dc3a34cd3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b82ffabf22c4782"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b680828a8614cde"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6d5e6b97512842b3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -28468,7 +28468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R780804af00994b87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re40cddfeedf743f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30036,7 +30036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11533b33b85a424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe553229524418f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30782,7 +30782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3abef46229004f34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966651a5aaef486c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31444,7 +31444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6c154e8e22c48f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa3ca930a8d941e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31588,7 +31588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6825ae928cf45e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc8c5eea125641fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32215,6 +32215,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R770015bf3a584910"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad2fcb287a64568"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Re8c4dd0368a24a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R3f38cfa91fb94d1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="Rcaeb400338e14175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R9645a6048c3b4807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R26949708fc884499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R865ff47078384e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rdeb6cd8dcec94ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R79e99725782d43ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R93bb1df144e14210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="Rb317d85cb65e434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R8630588780664a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R761add8e320342e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b82ffabf22c4782"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bb09a27aa934d83"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6d5e6b97512842b3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3baf6c8c24b94de8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -28468,7 +28468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re40cddfeedf743f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122b709ac6634bb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30036,7 +30036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafe553229524418f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7c2ee1d7e8466f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30782,7 +30782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966651a5aaef486c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71be9a11d21f4cfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31444,7 +31444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa3ca930a8d941e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39e9f75dbf04807"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31588,7 +31588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc8c5eea125641fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7e10868a6274ef9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32215,6 +32215,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad2fcb287a64568"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30dfeb22bec04a63"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rdeb6cd8dcec94ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R79e99725782d43ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R93bb1df144e14210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="Rb317d85cb65e434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R8630588780664a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R761add8e320342e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R48b14269e85a4910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rc14b26efb3ab480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="Rb02153e6e0484fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R0a156eb12163434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R11273aa5ac7f40e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R89a89ac289af4b48"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7bb09a27aa934d83"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R82e878a22410497c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3baf6c8c24b94de8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76961d619fcf47c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -28468,7 +28468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R122b709ac6634bb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107f17dca1f84008"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30036,7 +30036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7c2ee1d7e8466f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb19b60ceee334c9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30782,7 +30782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71be9a11d21f4cfd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ca7a8190d14514"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31444,7 +31444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39e9f75dbf04807"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb90e9cc680414255"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31588,7 +31588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7e10868a6274ef9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1801c136021d4290"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32215,6 +32215,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30dfeb22bec04a63"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90956cf46ca94be5"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R48b14269e85a4910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="Rc14b26efb3ab480f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="Rb02153e6e0484fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R0a156eb12163434c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R11273aa5ac7f40e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R89a89ac289af4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Rd49a3861d152485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R84a73760f58c4ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R7a22d8f7c7b0427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R5c76452990d94042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R59d5b582603540ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R388c873e72c74532"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R82e878a22410497c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rebaf92a711d349cd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R76961d619fcf47c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a46336ffad84c0f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -28468,7 +28468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107f17dca1f84008"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6c6bc68e194b40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30036,7 +30036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb19b60ceee334c9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1844ac8c608a458f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30782,7 +30782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ca7a8190d14514"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab91a4fc321645e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31444,7 +31444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb90e9cc680414255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref92d16c2e384c62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31588,7 +31588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1801c136021d4290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd46b7867cd8d488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32215,6 +32215,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90956cf46ca94be5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35e0f9d1790d499e"/>
 </x:worksheet>
 </file>
--- a/data/catalogo-agentes-operacionais-copilot.xlsx
+++ b/data/catalogo-agentes-operacionais-copilot.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="R412210b93cc94a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R75d8989f9c604251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R722f4a2fd26547b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R7ed19470e8ba4651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R79cf36d719414129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R1c81f0ff89214005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo de agentes" sheetId="1" r:id="Ra182eca2c5224fc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 40 demos" sheetId="2" r:id="R91d45eea19564a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cowork playbook" sheetId="3" r:id="R1d677a48ae7842a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes" sheetId="4" r:id="R9a55bc2393e64aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como escolher" sheetId="5" r:id="R0a10a6009e49413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="6" r:id="R003e4f811f71441d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R483a12b19c354101"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd2d8e755f73d41b4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -397,7 +397,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb035a5e9690d4466"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd51f508ebc624785"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -28468,7 +28468,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31ade8f78dbd455b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1355265746224fdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30036,7 +30036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e6a183ce1734c69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc121a0164ed4cbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30782,7 +30782,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e4eeb92471b4ea4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aa4e6d38f047a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31444,7 +31444,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re56f6fc3aa234452"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R024135ef65274852"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31588,7 +31588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b79b306b02b404c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dd6f06b03d14320"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32215,6 +32215,6 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ec90f1b2e24dd2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea3e675648a43ec"/>
 </x:worksheet>
 </file>